--- a/نمونه گزارش پرشده.xlsx
+++ b/نمونه گزارش پرشده.xlsx
@@ -11,6 +11,7 @@
     <sheet name="سوادرسانه مجازی (لایو)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="توانمندسازی گردان" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="اطلاعات پایه" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="تولیدات " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +502,6 @@
           <t>سالن شهید بهشتی</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -538,7 +538,6 @@
           <t>مسجد جامع</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -575,7 +574,6 @@
           <t>حسینیه</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -614,7 +612,6 @@
           <t>سالن اجتماعات</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -651,18 +648,11 @@
           <t>مدرسه</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -842,7 +832,6 @@
           <t>ایتا</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -945,7 +934,6 @@
           <t>پایگاه</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>حضوری</t>
@@ -987,7 +975,6 @@
           <t>پایگاه</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>حضوری</t>
@@ -1029,7 +1016,6 @@
           <t>پایگاه</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>حضوری</t>
@@ -1060,9 +1046,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1115,4 +1098,198 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>تاریخ محتوای تولید شده</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>تولید کننده</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>موضوع</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>نام تولید کننده محتوا</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>نوع تولید محتوا</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>تعداد صفحات</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>لینک مستندات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1405/06/06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ناحیه ۱</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>پوستر هفته دفاع مقدس</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>زهرا احمدی</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>پوستر</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1405/06/11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ناحیه ۲</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>کلیپ سواد رسانه</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>سعید نوری</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>کلیپ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1405/06/14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ناحیه ۱</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>اینفوگرافی اخبار جعلی</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>سعيد  نوري</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>اینفوگرافی</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1405/06/22</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ناحیه ۳</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>موشن‌گرافی جنگ شناختی</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>محمد رضایی</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>موشن</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>